--- a/inputdata/inputdata_standalone.xlsx
+++ b/inputdata/inputdata_standalone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74AE000-64E6-4565-B8DC-A4B98743D8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5FAC80-5663-48D9-BD43-1DA3FE77A830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -1185,9 +1185,6 @@
     <t>Use_Database_PV</t>
   </si>
   <si>
-    <t>N_modules</t>
-  </si>
-  <si>
     <t>Use_Database_Inv</t>
   </si>
   <si>
@@ -1219,6 +1216,9 @@
   </si>
   <si>
     <t>PV_Degradation_Rate</t>
+  </si>
+  <si>
+    <t>N_Modules</t>
   </si>
 </sst>
 </file>
@@ -9080,7 +9080,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C10" s="86">
         <v>25</v>
@@ -9097,7 +9097,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C11" s="20">
         <v>8.0000000000000002E-3</v>
@@ -9849,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C6" s="111">
         <v>10</v>
@@ -10214,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="110" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C4" s="111">
         <v>1</v>
@@ -10229,7 +10229,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C5" s="112" t="s">
         <v>291</v>
@@ -10844,7 +10844,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="110" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" s="111">
         <v>1</v>
@@ -10859,7 +10859,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C5" s="112" t="s">
         <v>292</v>
@@ -10874,7 +10874,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C6" s="111">
         <v>4</v>
@@ -11076,7 +11076,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="105" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C18" s="106">
         <v>0</v>
@@ -11093,7 +11093,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="105" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C19" s="106">
         <v>45</v>
@@ -11110,7 +11110,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="105" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C20" s="106">
         <v>-20</v>
@@ -11127,7 +11127,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="105" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C21" s="106">
         <v>60</v>

--- a/inputdata/inputdata_standalone.xlsx
+++ b/inputdata/inputdata_standalone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5FAC80-5663-48D9-BD43-1DA3FE77A830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80EB8C9-F77E-4155-B9A2-5F24C295D3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9100,7 +9100,7 @@
         <v>305</v>
       </c>
       <c r="C11" s="20">
-        <v>8.0000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>7</v>

--- a/inputdata/inputdata_standalone.xlsx
+++ b/inputdata/inputdata_standalone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80EB8C9-F77E-4155-B9A2-5F24C295D3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2381F9-1A13-434E-A595-C1679A970878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -9802,7 +9802,7 @@
         <v>294</v>
       </c>
       <c r="C4" s="111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="111"/>
       <c r="E4" s="110" t="s">
@@ -10217,7 +10217,7 @@
         <v>295</v>
       </c>
       <c r="C4" s="111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="111"/>
       <c r="E4" s="110" t="s">
@@ -10847,7 +10847,7 @@
         <v>297</v>
       </c>
       <c r="C4" s="111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="111"/>
       <c r="E4" s="110" t="s">
